--- a/reports/devops-juniors-israel-2026-W31.xlsx
+++ b/reports/devops-juniors-israel-2026-W31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="411">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27T10:07:11</t>
+    <t xml:space="preserve">2026-07-28T08:49:43</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -163,6 +163,24 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Infrastructure- Lab Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAST Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-infrastructure-lab-engineer-at-vast-data-4445154255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -196,919 +214,922 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML Software &amp; Infrastructure Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-software-infrastructure-engineer-student-position-at-mobileye-4443239639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2 - 240769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-240769-at-experis-israel-4434811963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36620)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445610633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
   </si>
   <si>
     <t xml:space="preserve">RAD</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-23</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-dialog-4442351473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Customer Support Rep- Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-customer-support-rep-student-at-bright-data-4440677972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-sela-4441038419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galooli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (28516)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445612586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Representative (35966)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445608573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4442372082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiberias, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-genie-4438491899</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2 - 240769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-240769-at-experis-israel-4434811963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36620)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445610633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4440132141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412563583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Customer Support Rep- Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-customer-support-rep-student-at-bright-data-4440677972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-sela-4441038419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galooli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tnuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תמיכה טכנית</t>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (35953)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-35953-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445603942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioView</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bioview-4440464462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית - מערכת Meteor</t>
   </si>
   <si>
     <t xml:space="preserve">StoreNext</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Representative (35966)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445608573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (28516)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445612586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425556403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4442372082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MindCrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-mindcrm-4442826734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioView</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bioview-4440464462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🔥 בודקי תוכנה מתחילים? – משרה מלאה בדרום הארץ לפניכם!🔥7529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tesnet Group Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%F0%9F%94%A5-%D7%91%D7%95%D7%93%D7%A7%D7%99-%D7%AA%D7%95%D7%9B%D7%A0%D7%94-%D7%9E%D7%AA%D7%97%D7%99%D7%9C%D7%99%D7%9D%3F-%E2%80%93-%D7%9E%D7%A9%D7%A8%D7%94-%D7%9E%D7%9C%D7%90%D7%94-%D7%91%D7%93%D7%A8%D7%95%D7%9D-%D7%94%D7%90%D7%A8%D7%A5-%D7%9C%D7%A4%D7%A0%D7%99%D7%9B%D7%9D%21%F0%9F%94%A57529-at-tesnet-group-ltd-4442592044</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-meteor-at-storenext-4440240961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LabOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-labos-4442830175</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineering Student</t>
@@ -1135,13 +1156,25 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
@@ -1150,43 +1183,34 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1347,7 +1371,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -1355,7 +1379,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1371,7 +1395,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10">
@@ -1453,7 +1477,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -1461,7 +1485,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1469,7 +1493,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -1477,7 +1501,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1503,7 +1527,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
@@ -1511,7 +1535,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1523,7 +1547,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1640,25 +1664,25 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1666,13 +1690,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1710,7 +1734,7 @@
         <v>27</v>
       </c>
       <c r="F6" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>69</v>
@@ -1722,7 +1746,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -1730,31 +1754,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3">
+        <v>83</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>81</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1762,31 +1786,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3">
+        <v>80</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="3">
-        <v>74</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1794,31 +1818,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>74</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="3">
-        <v>70</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1826,31 +1850,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="3">
+        <v>70</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3">
-        <v>68</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1858,13 +1882,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -1873,16 +1897,16 @@
         <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -1890,31 +1914,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3">
+        <v>66</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3">
-        <v>60</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -1922,31 +1946,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>60</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="3">
-        <v>57</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -1954,31 +1978,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3">
+        <v>57</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="3">
-        <v>52</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -1986,31 +2010,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3">
         <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -2018,13 +2042,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -2033,16 +2057,16 @@
         <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17">
@@ -2050,13 +2074,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
@@ -2065,16 +2089,16 @@
         <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -2082,13 +2106,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
@@ -2097,16 +2121,16 @@
         <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19">
@@ -2114,13 +2138,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -2129,16 +2153,16 @@
         <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="20">
@@ -2146,13 +2170,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -2161,16 +2185,16 @@
         <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21">
@@ -2178,13 +2202,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -2193,16 +2217,16 @@
         <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="22">
@@ -2210,31 +2234,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="3">
+        <v>36</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>34</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="23">
@@ -2242,31 +2266,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="3">
+        <v>32</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>30</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="24">
@@ -2274,31 +2298,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="3">
+        <v>32</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>30</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25">
@@ -2306,13 +2330,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -2321,16 +2345,16 @@
         <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26">
@@ -2338,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -2362,7 +2386,7 @@
         <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2402,7 +2426,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2415,7 +2439,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2430,22 +2454,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
@@ -2468,7 +2492,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2480,7 +2504,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -2503,7 +2527,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2515,7 +2539,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2526,42 +2550,42 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2573,7 +2597,7 @@
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2585,7 +2609,7 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -2602,13 +2626,13 @@
         <v>27</v>
       </c>
       <c r="E6" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2617,7 +2641,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -2625,153 +2649,153 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3">
+        <v>83</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>81</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>80</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3">
-        <v>74</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="K8" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>74</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3">
-        <v>70</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="K9" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="3">
+        <v>70</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="3">
-        <v>68</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
@@ -2780,173 +2804,173 @@
         <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="K11" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3">
+        <v>66</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="3">
-        <v>60</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="K12" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3">
+        <v>60</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="3">
-        <v>57</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K13" s="3">
-        <v>73</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="3">
-        <v>52</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="K14" s="3">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3">
         <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K15" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
@@ -2955,33 +2979,33 @@
         <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K16" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
@@ -2990,33 +3014,33 @@
         <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="K17" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
@@ -3025,33 +3049,33 @@
         <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K18" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
@@ -3060,33 +3084,33 @@
         <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="K19" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
@@ -3095,33 +3119,33 @@
         <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="K20" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -3130,138 +3154,138 @@
         <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="K21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3">
+        <v>36</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>34</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="K22" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="3">
+        <v>32</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>30</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="K23" s="3">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="3">
+        <v>32</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>30</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="K24" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -3270,33 +3294,33 @@
         <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K25" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -3308,7 +3332,7 @@
         <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
@@ -3317,56 +3341,56 @@
         <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="K26" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="K27" s="3">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
@@ -3375,138 +3399,138 @@
         <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>88</v>
+        <v>186</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="K30" s="3">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="K31" s="3">
-        <v>26</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3515,80 +3539,80 @@
         <v>23</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="K32" s="3">
-        <v>68</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>201</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>202</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>104</v>
+        <v>203</v>
       </c>
       <c r="K33" s="3">
-        <v>73</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>205</v>
+        <v>96</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>206</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
@@ -3597,161 +3621,161 @@
         <v>207</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="K34" s="3">
-        <v>8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
         <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="K36" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="K37" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="K38" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3760,33 +3784,33 @@
         <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K39" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3795,33 +3819,33 @@
         <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K40" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3830,57 +3854,57 @@
         <v>17</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="K41" s="3">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>245</v>
+        <v>166</v>
       </c>
       <c r="K42" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -3888,7 +3912,7 @@
         <v>246</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>247</v>
@@ -3900,33 +3924,33 @@
         <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K43" s="3">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>27</v>
@@ -3935,68 +3959,68 @@
         <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K44" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>253</v>
+        <v>123</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>254</v>
+        <v>124</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E45" s="3">
         <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="K45" s="3">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>229</v>
+        <v>153</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -4005,33 +4029,33 @@
         <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="K46" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -4040,57 +4064,57 @@
         <v>13</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="K47" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3">
         <v>13</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K48" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
@@ -4098,80 +4122,80 @@
         <v>270</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>126</v>
+        <v>271</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E49" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>245</v>
+        <v>102</v>
       </c>
       <c r="K49" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>274</v>
+        <v>123</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="3">
+        <v>12</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="3">
-        <v>10</v>
-      </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="J50" s="3" t="s">
-        <v>59</v>
+        <v>250</v>
       </c>
       <c r="K50" s="3">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>278</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4180,33 +4204,33 @@
         <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>281</v>
+        <v>65</v>
       </c>
       <c r="K51" s="3">
-        <v>34</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>163</v>
+        <v>283</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4215,33 +4239,33 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>71</v>
+        <v>287</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>285</v>
+        <v>174</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4250,33 +4274,33 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>288</v>
+        <v>76</v>
       </c>
       <c r="K53" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4285,10 +4309,10 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
@@ -4297,21 +4321,21 @@
         <v>291</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>59</v>
+        <v>292</v>
       </c>
       <c r="K54" s="3">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>286</v>
+        <v>129</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4320,33 +4344,33 @@
         <v>10</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="K55" s="3">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4355,33 +4379,33 @@
         <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="K56" s="3">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>296</v>
+        <v>204</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4390,54 +4414,54 @@
         <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K57" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>126</v>
+        <v>303</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>268</v>
+        <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="K58" s="3">
         <v>18</v>
@@ -4445,48 +4469,48 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>249</v>
+        <v>186</v>
       </c>
       <c r="K59" s="3">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>306</v>
+        <v>191</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4495,33 +4519,33 @@
         <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>83</v>
+        <v>255</v>
       </c>
       <c r="K60" s="3">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>229</v>
+        <v>96</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4530,33 +4554,33 @@
         <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="K61" s="3">
-        <v>11</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4565,33 +4589,33 @@
         <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4600,138 +4624,138 @@
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K63" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>317</v>
+        <v>72</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>194</v>
+        <v>73</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E64" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>320</v>
+        <v>241</v>
       </c>
       <c r="K64" s="3">
-        <v>57</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>67</v>
+        <v>325</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E65" s="3">
         <v>4</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K65" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>288</v>
+        <v>76</v>
       </c>
       <c r="K66" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>330</v>
+        <v>96</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4740,33 +4764,33 @@
         <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>257</v>
+        <v>145</v>
       </c>
       <c r="K67" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4775,33 +4799,33 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>337</v>
+        <v>145</v>
       </c>
       <c r="K68" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>74</v>
+        <v>272</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4810,19 +4834,19 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>337</v>
+        <v>237</v>
       </c>
       <c r="K69" s="3">
         <v>14</v>
@@ -4830,13 +4854,13 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>342</v>
+        <v>137</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>268</v>
+        <v>345</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4845,33 +4869,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="K70" s="3">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4880,10 +4904,10 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
@@ -4892,21 +4916,21 @@
         <v>349</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="K71" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>258</v>
+        <v>350</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>351</v>
+        <v>96</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4915,10 +4939,10 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>31</v>
@@ -4927,21 +4951,21 @@
         <v>352</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>71</v>
+        <v>353</v>
       </c>
       <c r="K72" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>192</v>
+        <v>354</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>353</v>
+        <v>179</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -4950,33 +4974,33 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K73" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>192</v>
+        <v>356</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>25</v>
@@ -4985,33 +5009,33 @@
         <v>3</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>71</v>
+        <v>269</v>
       </c>
       <c r="K74" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>194</v>
+        <v>51</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>25</v>
@@ -5020,92 +5044,164 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>360</v>
+        <v>65</v>
       </c>
       <c r="K75" s="3">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>361</v>
+        <v>204</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="G76" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="K76" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>126</v>
+        <v>367</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="D77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="3">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K77" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="3">
+        <v>3</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K78" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E79" s="3">
         <v>0</v>
       </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="J77" s="3" t="s">
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J79" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="K77" s="3">
-        <v>63</v>
+      <c r="K79" s="3">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K77"/>
+  <autoFilter ref="A1:K79"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5183,6 +5279,8 @@
     <hyperlink ref="I75" r:id="rId74"/>
     <hyperlink ref="I76" r:id="rId75"/>
     <hyperlink ref="I77" r:id="rId76"/>
+    <hyperlink ref="I78" r:id="rId77"/>
+    <hyperlink ref="I79" r:id="rId78"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5190,9 +5288,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5213,10 +5311,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -5224,213 +5322,144 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>179</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>258</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>279</v>
+        <v>97</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>283</v>
+        <v>98</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>313</v>
+        <v>355</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>178</v>
+        <v>370</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>315</v>
+        <v>371</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5438,9 +5467,6 @@
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5455,35 +5481,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
@@ -5491,142 +5517,142 @@
         <v>322</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>373</v>
+        <v>248</v>
       </c>
       <c r="B5" s="3">
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>381</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>340</v>
+        <v>387</v>
       </c>
       <c r="B10" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -5646,10 +5672,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
@@ -5657,10 +5683,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3">
@@ -5668,10 +5694,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4">
@@ -5679,10 +5705,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5">
@@ -5690,10 +5716,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6">
@@ -5704,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -5725,13 +5751,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2">
@@ -5739,10 +5765,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5751,22 +5777,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W31.xlsx
+++ b/reports/devops-juniors-israel-2026-W31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="453">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28T08:49:43</t>
+    <t xml:space="preserve">2026-07-29T08:54:18</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -115,6 +115,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -163,108 +166,189 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Infrastructure- Lab Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAST Data</t>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NSO Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-systems-engineer-at-nso-group-4443299999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CertifyOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bar-Ilan University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-bar-ilan-university-4446564670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives Intralogistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-intralogistics-4446042176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-infrastructure-lab-engineer-at-vast-data-4445154255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
   </si>
   <si>
@@ -289,6 +373,15 @@
     <t xml:space="preserve">2026-07-21</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anecdotes</t>
   </si>
   <si>
@@ -301,18 +394,6 @@
     <t xml:space="preserve">2026-06-18</t>
   </si>
   <si>
-    <t xml:space="preserve">ML Software &amp; Infrastructure Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-software-infrastructure-engineer-student-position-at-mobileye-4443239639</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
   </si>
   <si>
@@ -322,9 +403,6 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -340,672 +418,747 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
+    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36620)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445610633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4443683633</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer – Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-%E2%80%93-student-position-at-upwind-security-4442537909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiberias, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galooli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4445499098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tnuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreNext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-1-at-abra-4445721784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support &amp; Field Implementation Coordinator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-field-implementation-coordinator-at-tondo-4443681583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Representative (35966)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445608573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2 - 240769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-240769-at-experis-israel-4434811963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36620)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445610633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Customer Support Rep- Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-customer-support-rep-student-at-bright-data-4440677972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-sela-4441038419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galooli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (28516)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-28516-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445612586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Representative (35966)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445608573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
-  </si>
-  <si>
     <t xml:space="preserve">טכנאי/ת Help desk</t>
   </si>
   <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
     <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
   </si>
   <si>
@@ -1015,13 +1168,10 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4442372082</t>
   </si>
   <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+    <t xml:space="preserve">Help Desk טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-genie-4438491899</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Technician</t>
@@ -1036,15 +1186,45 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
   </si>
   <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LabOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-labos-4442830175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית - מערכת Meteor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-meteor-at-storenext-4440240961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-support-engineer-at-configo-4442822566</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Technician (Student Position)</t>
   </si>
   <si>
     <t xml:space="preserve">Log-On Software</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
   </si>
   <si>
@@ -1057,79 +1237,28 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiberias, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-genie-4438491899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (35953)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-35953-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445603942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioView</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bioview-4440464462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תמיכה טכנית - מערכת Meteor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StoreNext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-meteor-at-storenext-4440240961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-labos-4442830175</t>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔥 בודקי תוכנה מתחילים? – משרה מלאה בדרום הארץ לפניכם!🔥7529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesnet Group Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%F0%9F%94%A5-%D7%91%D7%95%D7%93%D7%A7%D7%99-%D7%AA%D7%95%D7%9B%D7%A0%D7%94-%D7%9E%D7%AA%D7%97%D7%99%D7%9C%D7%99%D7%9D%3F-%E2%80%93-%D7%9E%D7%A9%D7%A8%D7%94-%D7%9E%D7%9C%D7%90%D7%94-%D7%91%D7%93%D7%A8%D7%95%D7%9D-%D7%94%D7%90%D7%A8%D7%A5-%D7%9C%D7%A4%D7%A0%D7%99%D7%9B%D7%9D%21%F0%9F%94%A57529-at-tesnet-group-ltd-4442592044</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineering Student</t>
@@ -1159,34 +1288,52 @@
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -1195,24 +1342,6 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -1244,9 +1373,6 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1497,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -1379,7 +1505,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1387,7 +1513,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1395,7 +1521,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>554</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10">
@@ -1477,7 +1603,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -1485,7 +1611,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1493,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -1501,7 +1627,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1527,7 +1653,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29">
@@ -1535,7 +1661,15 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>9</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1547,7 +1681,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1559,34 +1693,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1594,13 +1728,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>29</v>
@@ -1609,16 +1743,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1626,13 +1760,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>28</v>
@@ -1641,16 +1775,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1658,16 +1792,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1696,7 +1830,7 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1705,16 +1839,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1722,13 +1856,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
@@ -1737,16 +1871,16 @@
         <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1754,13 +1888,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1769,16 +1903,16 @@
         <v>83</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1786,31 +1920,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1818,31 +1952,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -1850,31 +1984,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -1882,31 +2016,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1914,31 +2048,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="3">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1946,31 +2080,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -1978,31 +2112,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -2010,31 +2144,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -2042,31 +2176,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -2074,31 +2208,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
@@ -2106,31 +2240,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -2138,31 +2272,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
@@ -2170,31 +2304,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>51</v>
+        <v>136</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
@@ -2202,31 +2336,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
@@ -2234,31 +2368,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23">
@@ -2266,31 +2400,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>147</v>
+        <v>45</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24">
@@ -2298,31 +2432,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>154</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
@@ -2330,31 +2464,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
@@ -2362,19 +2496,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>164</v>
@@ -2426,7 +2560,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2442,16 +2576,16 @@
         <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>168</v>
@@ -2460,13 +2594,13 @@
         <v>169</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>171</v>
@@ -2474,13 +2608,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>29</v>
@@ -2489,7 +2623,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>172</v>
@@ -2498,24 +2632,24 @@
         <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>28</v>
@@ -2524,7 +2658,7 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>172</v>
@@ -2533,27 +2667,27 @@
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2574,7 +2708,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -2585,7 +2719,7 @@
         <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2594,7 +2728,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>172</v>
@@ -2603,24 +2737,24 @@
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>27</v>
@@ -2629,7 +2763,7 @@
         <v>92</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>172</v>
@@ -2638,24 +2772,24 @@
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
@@ -2664,7 +2798,7 @@
         <v>83</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>172</v>
@@ -2673,33 +2807,33 @@
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>172</v>
@@ -2708,68 +2842,68 @@
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="K9" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>172</v>
@@ -2778,33 +2912,33 @@
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="K10" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>172</v>
@@ -2813,33 +2947,33 @@
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E12" s="3">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>172</v>
@@ -2848,68 +2982,68 @@
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="K13" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>172</v>
@@ -2918,33 +3052,33 @@
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K14" s="3">
-        <v>74</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>172</v>
@@ -2953,138 +3087,138 @@
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K15" s="3">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="K16" s="3">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K17" s="3">
-        <v>70</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="K18" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>172</v>
@@ -3093,33 +3227,33 @@
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K19" s="3">
-        <v>4</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>136</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>172</v>
@@ -3128,33 +3262,33 @@
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K20" s="3">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>172</v>
@@ -3163,68 +3297,68 @@
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K21" s="3">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="K22" s="3">
-        <v>15</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>147</v>
+        <v>45</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>172</v>
@@ -3233,30 +3367,30 @@
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="K23" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>154</v>
@@ -3265,36 +3399,36 @@
         <v>172</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="K24" s="3">
-        <v>4</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>172</v>
@@ -3303,30 +3437,30 @@
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="K25" s="3">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>164</v>
@@ -3344,7 +3478,7 @@
         <v>166</v>
       </c>
       <c r="K26" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -3352,124 +3486,124 @@
         <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>37</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>30</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="K27" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>37</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="3">
-        <v>28</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>34</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="3">
-        <v>28</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="K29" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>187</v>
+        <v>94</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>172</v>
@@ -3478,83 +3612,83 @@
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="K30" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>30</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="3">
-        <v>24</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="K31" s="3">
-        <v>74</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>30</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>23</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="K32" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -3565,13 +3699,13 @@
         <v>200</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>51</v>
+        <v>195</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>201</v>
@@ -3586,135 +3720,135 @@
         <v>202</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="K33" s="3">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>28</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>23</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="K34" s="3">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3">
+        <v>27</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>20</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K35" s="3">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>27</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>20</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="K36" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>172</v>
@@ -3723,33 +3857,33 @@
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="K37" s="3">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>172</v>
@@ -3758,33 +3892,33 @@
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="K38" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>172</v>
@@ -3793,33 +3927,33 @@
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="K39" s="3">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>172</v>
@@ -3828,173 +3962,173 @@
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K40" s="3">
-        <v>14</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>241</v>
+        <v>133</v>
       </c>
       <c r="K41" s="3">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>20</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>17</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="K42" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>20</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43" s="3">
-        <v>13</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>250</v>
+        <v>66</v>
       </c>
       <c r="K43" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3">
+        <v>20</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="3">
-        <v>13</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="K44" s="3">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>172</v>
@@ -4003,33 +4137,33 @@
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K45" s="3">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>153</v>
+        <v>260</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>172</v>
@@ -4038,34 +4172,34 @@
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>102</v>
+        <v>263</v>
       </c>
       <c r="K46" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>13</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>172</v>
       </c>
@@ -4073,33 +4207,33 @@
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="K47" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>172</v>
@@ -4108,24 +4242,24 @@
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K48" s="3">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>271</v>
+        <v>68</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>27</v>
@@ -4134,43 +4268,43 @@
         <v>13</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K49" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="3">
+        <v>13</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="3">
-        <v>12</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="G50" s="3" t="s">
         <v>172</v>
       </c>
@@ -4178,45 +4312,45 @@
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="K50" s="3">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>278</v>
+        <v>158</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>281</v>
-      </c>
       <c r="J51" s="3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K51" s="3">
         <v>65</v>
@@ -4224,57 +4358,57 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="3">
-        <v>10</v>
-      </c>
-      <c r="F52" s="3" t="s">
+      <c r="G52" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>286</v>
-      </c>
       <c r="J52" s="3" t="s">
-        <v>287</v>
+        <v>121</v>
       </c>
       <c r="K52" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>174</v>
+        <v>287</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>13</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>10</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>172</v>
@@ -4286,30 +4420,30 @@
         <v>289</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>172</v>
@@ -4321,91 +4455,91 @@
         <v>291</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>292</v>
+        <v>99</v>
       </c>
       <c r="K54" s="3">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="3">
+        <v>12</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="G55" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>10</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>296</v>
+        <v>105</v>
       </c>
       <c r="K55" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="3">
+        <v>12</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="3">
-        <v>10</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="J56" s="3" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="K56" s="3">
-        <v>65</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4414,33 +4548,33 @@
         <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="K57" s="3">
-        <v>4</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4449,7 +4583,7 @@
         <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>172</v>
@@ -4458,34 +4592,34 @@
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>140</v>
+        <v>308</v>
       </c>
       <c r="K58" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E59" s="3">
-        <v>8</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>172</v>
       </c>
@@ -4493,33 +4627,33 @@
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>186</v>
+        <v>312</v>
       </c>
       <c r="K59" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>191</v>
+        <v>314</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>172</v>
@@ -4528,33 +4662,33 @@
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="K60" s="3">
-        <v>50</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>96</v>
+        <v>319</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>172</v>
@@ -4563,33 +4697,33 @@
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>316</v>
+        <v>66</v>
       </c>
       <c r="K61" s="3">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>179</v>
+        <v>304</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>175</v>
+        <v>305</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>172</v>
@@ -4598,33 +4732,33 @@
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K62" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>319</v>
+        <v>108</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>172</v>
@@ -4633,68 +4767,68 @@
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="K63" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>73</v>
+        <v>212</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E64" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="K64" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>172</v>
@@ -4703,30 +4837,30 @@
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>237</v>
+        <v>333</v>
       </c>
       <c r="K65" s="3">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>331</v>
@@ -4738,33 +4872,33 @@
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K66" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>96</v>
+        <v>260</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>172</v>
@@ -4773,33 +4907,33 @@
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="K67" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E68" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>172</v>
@@ -4808,33 +4942,33 @@
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>145</v>
+        <v>345</v>
       </c>
       <c r="K68" s="3">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>272</v>
+        <v>81</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E69" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>172</v>
@@ -4843,33 +4977,33 @@
         <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>237</v>
+        <v>66</v>
       </c>
       <c r="K69" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>137</v>
+        <v>348</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>345</v>
+        <v>63</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E70" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>172</v>
@@ -4878,33 +5012,33 @@
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>241</v>
+        <v>66</v>
       </c>
       <c r="K70" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E71" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>172</v>
@@ -4913,33 +5047,33 @@
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="K71" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>351</v>
+        <v>204</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E72" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>172</v>
@@ -4948,33 +5082,33 @@
         <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>353</v>
+        <v>78</v>
       </c>
       <c r="K72" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>179</v>
+        <v>358</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E73" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>172</v>
@@ -4983,68 +5117,68 @@
         <v>31</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>54</v>
+        <v>361</v>
       </c>
       <c r="K73" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>357</v>
+        <v>74</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>358</v>
+        <v>75</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E74" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>172</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K74" s="3">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>204</v>
+        <v>365</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>51</v>
+        <v>367</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E75" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>172</v>
@@ -5053,24 +5187,24 @@
         <v>31</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="K75" s="3">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>204</v>
+        <v>371</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>25</v>
@@ -5079,7 +5213,7 @@
         <v>3</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>172</v>
@@ -5088,24 +5222,24 @@
         <v>31</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="K76" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>25</v>
@@ -5114,7 +5248,7 @@
         <v>3</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>172</v>
@@ -5123,24 +5257,24 @@
         <v>31</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>166</v>
+        <v>379</v>
       </c>
       <c r="K77" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>370</v>
+        <v>248</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>153</v>
+        <v>381</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>25</v>
@@ -5149,7 +5283,7 @@
         <v>3</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>342</v>
+        <v>382</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>172</v>
@@ -5158,50 +5292,396 @@
         <v>31</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="K78" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>123</v>
+        <v>248</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>124</v>
+        <v>249</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="3">
+        <v>3</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K79" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" s="3">
+        <v>3</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="K80" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K81" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="3">
+        <v>3</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K82" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K83" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" s="3">
+        <v>3</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" s="3">
+        <v>3</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K85" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86" s="3">
+        <v>3</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="K86" s="3">
         <v>27</v>
       </c>
-      <c r="E79" s="3">
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E87" s="3">
         <v>0</v>
       </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K79" s="3">
-        <v>64</v>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E88" s="3">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K88" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K89" s="3">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K79"/>
+  <autoFilter ref="A1:K89"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5281,6 +5761,16 @@
     <hyperlink ref="I77" r:id="rId76"/>
     <hyperlink ref="I78" r:id="rId77"/>
     <hyperlink ref="I79" r:id="rId78"/>
+    <hyperlink ref="I80" r:id="rId79"/>
+    <hyperlink ref="I81" r:id="rId80"/>
+    <hyperlink ref="I82" r:id="rId81"/>
+    <hyperlink ref="I83" r:id="rId82"/>
+    <hyperlink ref="I84" r:id="rId83"/>
+    <hyperlink ref="I85" r:id="rId84"/>
+    <hyperlink ref="I86" r:id="rId85"/>
+    <hyperlink ref="I87" r:id="rId86"/>
+    <hyperlink ref="I88" r:id="rId87"/>
+    <hyperlink ref="I89" r:id="rId88"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5288,9 +5778,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5299,16 +5789,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>168</v>
@@ -5317,149 +5807,308 @@
         <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="3">
+        <v>74</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>354</v>
+        <v>149</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>179</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>342</v>
+        <v>150</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>355</v>
+        <v>151</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>369</v>
+        <v>177</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>370</v>
+        <v>211</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>54</v>
+      <c r="E13" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5467,6 +6116,13 @@
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
+    <hyperlink ref="F13" r:id="rId12"/>
+    <hyperlink ref="F14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5481,178 +6137,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>379</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>380</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>382</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>361</v>
+        <v>427</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>385</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>388</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>275</v>
+        <v>382</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>389</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>331</v>
+        <v>293</v>
       </c>
       <c r="B12" s="3">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>390</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>392</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>393</v>
+        <v>436</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>396</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>397</v>
+        <v>440</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>398</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -5669,13 +6325,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>442</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>400</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
@@ -5683,10 +6339,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>401</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3">
@@ -5694,10 +6350,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>402</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4">
@@ -5705,10 +6361,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>403</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5">
@@ -5716,10 +6372,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>404</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6">
@@ -5730,7 +6386,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>405</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -5748,16 +6404,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>408</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2">
@@ -5765,10 +6421,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5777,22 +6433,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>410</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W31.xlsx
+++ b/reports/devops-juniors-israel-2026-W31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29T08:54:18</t>
+    <t xml:space="preserve">2026-07-30T08:45:04</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -148,6 +148,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
   </si>
   <si>
@@ -199,106 +217,580 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NSO Group</t>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-systems-engineer-at-nso-group-4443299999</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CertifyOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-dialog-4442351473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CertifyOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bar-Ilan University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-bar-ilan-university-4446564670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer – Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-%E2%80%93-student-position-at-upwind-security-4442537909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Customer Support Rep- Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-customer-support-rep-student-at-bright-data-4440677972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
@@ -307,1039 +799,439 @@
     <t xml:space="preserve">Ashdod, South District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives Intralogistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-intralogistics-4446042176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webox LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4443675782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4444112385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (35966 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-1-at-abra-4445721784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tnuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreNext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astreya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-astreya-4446069583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-support-engineer-at-jobgether-4444104629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
   </si>
   <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36620)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445610633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4443683633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer – Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-%E2%80%93-student-position-at-upwind-security-4442537909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiberias, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4444118425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LabOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-labos-4442830175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galooli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4445499098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tnuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StoreNext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-1-at-abra-4445721784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support &amp; Field Implementation Coordinator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tondo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-field-implementation-coordinator-at-tondo-4443681583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Representative (35966)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-representative-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445608573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4442372082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-genie-4438491899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-labos-4442830175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תמיכה טכנית - מערכת Meteor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-meteor-at-storenext-4440240961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-support-engineer-at-configo-4442822566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🔥 בודקי תוכנה מתחילים? – משרה מלאה בדרום הארץ לפניכם!🔥7529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tesnet Group Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%F0%9F%94%A5-%D7%91%D7%95%D7%93%D7%A7%D7%99-%D7%AA%D7%95%D7%9B%D7%A0%D7%94-%D7%9E%D7%AA%D7%97%D7%99%D7%9C%D7%99%D7%9D%3F-%E2%80%93-%D7%9E%D7%A9%D7%A8%D7%94-%D7%9E%D7%9C%D7%90%D7%94-%D7%91%D7%93%D7%A8%D7%95%D7%9D-%D7%94%D7%90%D7%A8%D7%A5-%D7%9C%D7%A4%D7%A0%D7%99%D7%9B%D7%9D%21%F0%9F%94%A57529-at-tesnet-group-ltd-4442592044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1497,7 +1389,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -1505,7 +1397,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1513,7 +1405,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -1521,7 +1413,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>567</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10">
@@ -1603,7 +1495,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -1611,7 +1503,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1619,7 +1511,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -1653,7 +1545,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -1661,7 +1553,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -1681,7 +1573,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1737,7 +1629,7 @@
         <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1746,7 +1638,7 @@
         <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>48</v>
@@ -1769,7 +1661,7 @@
         <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1798,25 +1690,25 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1824,13 +1716,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1865,16 +1757,16 @@
         <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>71</v>
@@ -1894,25 +1786,25 @@
         <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1920,31 +1812,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="3">
+        <v>83</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="3">
-        <v>81</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1952,13 +1844,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1967,16 +1859,16 @@
         <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -1984,31 +1876,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -2016,31 +1908,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -2048,19 +1940,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>103</v>
@@ -2080,31 +1972,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
@@ -2112,31 +2004,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F14" s="3">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -2144,31 +2036,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F15" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -2176,31 +2068,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17">
@@ -2208,31 +2100,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -2240,31 +2132,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -2272,31 +2164,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -2304,31 +2196,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -2336,31 +2228,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22">
@@ -2368,31 +2260,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -2400,31 +2292,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24">
@@ -2432,31 +2324,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25">
@@ -2464,31 +2356,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
@@ -2496,31 +2388,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2573,7 +2465,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2588,22 +2480,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2617,7 +2509,7 @@
         <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2626,10 +2518,10 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>48</v>
@@ -2638,7 +2530,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2652,7 +2544,7 @@
         <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2661,7 +2553,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2673,7 +2565,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -2684,42 +2576,42 @@
         <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="3">
         <v>58</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K4" s="3">
-        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2731,7 +2623,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2743,7 +2635,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -2757,19 +2649,19 @@
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>71</v>
@@ -2778,7 +2670,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -2789,28 +2681,28 @@
         <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="K7" s="3">
         <v>2</v>
@@ -2818,48 +2710,48 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3">
+        <v>83</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3">
-        <v>81</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="K8" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2868,115 +2760,115 @@
         <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K11" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
@@ -2988,1640 +2880,1640 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E14" s="3">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K15" s="3">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K16" s="3">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="K17" s="3">
-        <v>41</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="K18" s="3">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K21" s="3">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="K22" s="3">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="K24" s="3">
-        <v>71</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="K25" s="3">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K26" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="K27" s="3">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>122</v>
+        <v>186</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="K28" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="K29" s="3">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="K30" s="3">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="K31" s="3">
-        <v>30</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="K32" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="K33" s="3">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K34" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="K35" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>212</v>
+        <v>97</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>66</v>
+        <v>227</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="K37" s="3">
-        <v>75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E38" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="K38" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>224</v>
+        <v>136</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>110</v>
+        <v>238</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>227</v>
+        <v>66</v>
       </c>
       <c r="K39" s="3">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>232</v>
+        <v>55</v>
       </c>
       <c r="K40" s="3">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="3">
+        <v>13</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>20</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="G41" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>133</v>
+        <v>244</v>
       </c>
       <c r="K41" s="3">
-        <v>75</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>240</v>
+        <v>156</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="K42" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>91</v>
+        <v>251</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E44" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K44" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E45" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K45" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>263</v>
+        <v>66</v>
       </c>
       <c r="K46" s="3">
-        <v>15</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>198</v>
+        <v>273</v>
       </c>
       <c r="K47" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>271</v>
+        <v>49</v>
       </c>
       <c r="K48" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>68</v>
+        <v>276</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="K49" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>158</v>
+        <v>279</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>277</v>
+        <v>167</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K50" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>158</v>
+        <v>283</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>49</v>
+        <v>285</v>
       </c>
       <c r="K51" s="3">
-        <v>65</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>281</v>
+        <v>101</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>283</v>
+        <v>92</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="K52" s="3">
-        <v>14</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="K53" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>96</v>
+        <v>256</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>99</v>
+        <v>295</v>
       </c>
       <c r="K54" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>283</v>
+        <v>97</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>105</v>
+        <v>244</v>
       </c>
       <c r="K55" s="3">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>94</v>
+        <v>299</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>99</v>
+        <v>303</v>
       </c>
       <c r="K56" s="3">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>301</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K57" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>308</v>
+        <v>49</v>
       </c>
       <c r="K58" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>310</v>
+        <v>182</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
@@ -4630,196 +4522,196 @@
         <v>311</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>312</v>
+        <v>89</v>
       </c>
       <c r="K59" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="3">
-        <v>10</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="J60" s="3" t="s">
-        <v>180</v>
+        <v>291</v>
       </c>
       <c r="K60" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>319</v>
+        <v>69</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>301</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>305</v>
+        <v>156</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>113</v>
+        <v>291</v>
       </c>
       <c r="K62" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="K63" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>6</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E64" s="3">
-        <v>8</v>
-      </c>
-      <c r="F64" s="3" t="s">
+      <c r="G64" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>328</v>
-      </c>
       <c r="J64" s="3" t="s">
-        <v>329</v>
+        <v>49</v>
       </c>
       <c r="K64" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>80</v>
+        <v>329</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4828,92 +4720,92 @@
         <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
+      <c r="J65" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>333</v>
-      </c>
       <c r="K65" s="3">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="G66" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="3">
-        <v>6</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>336</v>
-      </c>
       <c r="J66" s="3" t="s">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="K66" s="3">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" s="3">
+        <v>4</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="3">
-        <v>6</v>
-      </c>
-      <c r="F67" s="3" t="s">
+      <c r="G67" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" s="3" t="s">
+      <c r="J67" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="J67" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="K67" s="3">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68">
@@ -4924,19 +4816,19 @@
         <v>342</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E68" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>343</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
@@ -4945,33 +4837,33 @@
         <v>344</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>345</v>
+        <v>223</v>
       </c>
       <c r="K68" s="3">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="C69" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E69" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>343</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>31</v>
@@ -4980,231 +4872,231 @@
         <v>347</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>66</v>
+        <v>348</v>
       </c>
       <c r="K69" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="J70" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="3">
-        <v>6</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>352</v>
+        <v>256</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E71" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
       <c r="K71" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>6</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="G72" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="K72" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>52</v>
+        <v>325</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E73" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>361</v>
+        <v>95</v>
       </c>
       <c r="K73" s="3">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>74</v>
+        <v>364</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E74" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="K74" s="3">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>365</v>
+        <v>195</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>366</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="3">
+        <v>3</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E75" s="3">
-        <v>4</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>369</v>
-      </c>
       <c r="J75" s="3" t="s">
-        <v>370</v>
+        <v>66</v>
       </c>
       <c r="K75" s="3">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>367</v>
+        <v>216</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>25</v>
@@ -5213,33 +5105,33 @@
         <v>3</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="K76" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>25</v>
@@ -5248,440 +5140,92 @@
         <v>3</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>379</v>
+        <v>77</v>
       </c>
       <c r="K77" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>248</v>
+        <v>374</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E78" s="3">
-        <v>3</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>382</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K78" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>248</v>
+        <v>136</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>249</v>
+        <v>137</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E79" s="3">
-        <v>3</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>382</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>198</v>
+        <v>55</v>
       </c>
       <c r="K79" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E80" s="3">
-        <v>3</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="K80" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E81" s="3">
-        <v>3</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K81" s="3">
         <v>66</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E82" s="3">
-        <v>3</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K82" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E83" s="3">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K83" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E84" s="3">
-        <v>3</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E85" s="3">
-        <v>3</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="K85" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E86" s="3">
-        <v>3</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="K86" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E87" s="3">
-        <v>0</v>
-      </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E88" s="3">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K88" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K89" s="3">
-        <v>65</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K89"/>
+  <autoFilter ref="A1:K79"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5761,16 +5305,6 @@
     <hyperlink ref="I77" r:id="rId76"/>
     <hyperlink ref="I78" r:id="rId77"/>
     <hyperlink ref="I79" r:id="rId78"/>
-    <hyperlink ref="I80" r:id="rId79"/>
-    <hyperlink ref="I81" r:id="rId80"/>
-    <hyperlink ref="I82" r:id="rId81"/>
-    <hyperlink ref="I83" r:id="rId82"/>
-    <hyperlink ref="I84" r:id="rId83"/>
-    <hyperlink ref="I85" r:id="rId84"/>
-    <hyperlink ref="I86" r:id="rId85"/>
-    <hyperlink ref="I87" r:id="rId86"/>
-    <hyperlink ref="I88" r:id="rId87"/>
-    <hyperlink ref="I89" r:id="rId88"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5778,9 +5312,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5801,10 +5335,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -5812,10 +5346,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
@@ -5824,291 +5358,178 @@
         <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>245</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>274</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>88</v>
+        <v>271</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>275</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>278</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>92</v>
+        <v>280</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>281</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>106</v>
+        <v>304</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>103</v>
+        <v>301</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>107</v>
+        <v>306</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>149</v>
+        <v>307</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>308</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>150</v>
+        <v>297</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>151</v>
+        <v>309</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>213</v>
+        <v>301</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>214</v>
+        <v>322</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>243</v>
+        <v>323</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>244</v>
+        <v>324</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>246</v>
+        <v>327</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3">
-        <v>6</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>6</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="3">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="3">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -6118,11 +5539,6 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
-    <hyperlink ref="F13" r:id="rId12"/>
-    <hyperlink ref="F14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -6137,178 +5553,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>379</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>418</v>
+        <v>380</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>419</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>420</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>421</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="B4" s="3">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>422</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="B5" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>423</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>424</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>425</v>
+        <v>387</v>
       </c>
       <c r="B7" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>426</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>427</v>
+        <v>351</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B9" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>429</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>430</v>
+        <v>392</v>
       </c>
       <c r="B10" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>431</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B11" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>293</v>
+        <v>396</v>
       </c>
       <c r="B12" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="B13" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>438</v>
+        <v>402</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>440</v>
+        <v>404</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>441</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -6328,10 +5744,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>442</v>
+        <v>406</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>443</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
@@ -6339,10 +5755,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3">
@@ -6350,10 +5766,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>445</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4">
@@ -6361,10 +5777,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>446</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5">
@@ -6375,7 +5791,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>447</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6">
@@ -6386,7 +5802,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>448</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -6407,13 +5823,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>451</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2">
@@ -6421,10 +5837,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -6433,10 +5849,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -6448,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W31.xlsx
+++ b/reports/devops-juniors-israel-2026-W31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30T08:45:04</t>
+    <t xml:space="preserve">2026-07-31T09:15:18</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -235,6 +235,24 @@
     <t xml:space="preserve">2026-07-23</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
   </si>
   <si>
@@ -250,6 +268,24 @@
     <t xml:space="preserve">2026-07-28</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer – Test Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4446757352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devops Student</t>
   </si>
   <si>
@@ -286,30 +322,72 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Student</t>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
   </si>
   <si>
     <t xml:space="preserve">Radware</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
   </si>
   <si>
     <t xml:space="preserve">Dialog</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -319,21 +397,6 @@
     <t xml:space="preserve">2026-07-26</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
   </si>
   <si>
@@ -361,67 +424,421 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-29</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seemplicity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-e2e-solutions-il-4446785033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 24376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-24376-at-comblack-4446756706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enlight Renewable Energy Ltd (ENLT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-enlight-renewable-energy-ltd-enlt-4442705417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4444559393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
@@ -430,774 +847,330 @@
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webox LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4443675782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (34817 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446725424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4444563403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tnuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreNext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (35966 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4444112385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYMOTIVE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer – Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-%E2%80%93-student-position-at-upwind-security-4442537909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+    <t xml:space="preserve">Astreya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-astreya-4446069583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-1-at-abra-4445721784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Customer Support Rep- Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-customer-support-rep-student-at-bright-data-4440677972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת Help Desk Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webox LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-help-desk-tier-1-at-webox-ltd-4443675782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4444112385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (35966 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-1-at-abra-4445721784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tnuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StoreNext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astreya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-astreya-4446069583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-support-engineer-at-jobgether-4444104629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4444118425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-labos-4442830175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
@@ -1216,6 +1189,12 @@
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -1226,12 +1205,6 @@
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1389,7 +1362,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -1397,7 +1370,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1405,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -1413,7 +1386,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>575</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10">
@@ -1495,7 +1468,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -1503,7 +1476,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1511,7 +1484,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1545,7 +1518,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1553,7 +1526,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1786,25 +1759,25 @@
         <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1812,19 +1785,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>81</v>
@@ -1853,16 +1826,16 @@
         <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>88</v>
@@ -1888,13 +1861,13 @@
         <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>94</v>
@@ -1908,31 +1881,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -1940,31 +1913,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -1972,31 +1945,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
@@ -2004,31 +1977,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -2036,31 +2009,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -2068,31 +2041,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -2100,19 +2073,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>128</v>
@@ -2124,7 +2097,7 @@
         <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18">
@@ -2132,31 +2105,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
@@ -2164,31 +2137,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -2196,31 +2169,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
@@ -2228,31 +2201,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -2260,31 +2233,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23">
@@ -2292,19 +2265,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>157</v>
@@ -2316,7 +2289,7 @@
         <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>159</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24">
@@ -2324,31 +2297,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="3">
+        <v>44</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>30</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="25">
@@ -2356,31 +2329,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3">
+        <v>44</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>30</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>170</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26">
@@ -2388,31 +2361,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>37</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>27</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2451,8 +2424,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2465,7 +2438,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2480,22 +2453,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2518,7 +2491,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2530,7 +2503,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2526,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2565,7 +2538,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -2588,7 +2561,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2600,7 +2573,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -2623,7 +2596,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2635,7 +2608,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2631,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2670,7 +2643,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2681,54 +2654,54 @@
         <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2754,19 +2727,19 @@
         <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>88</v>
@@ -2775,7 +2748,7 @@
         <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2792,16 +2765,16 @@
         <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>94</v>
@@ -2810,240 +2783,240 @@
         <v>95</v>
       </c>
       <c r="K10" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K11" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K12" s="3">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K13" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>76</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K15" s="3">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -3052,208 +3025,208 @@
         <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K17" s="3">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K21" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>89</v>
       </c>
       <c r="K22" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
@@ -3262,593 +3235,593 @@
         <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>159</v>
+        <v>101</v>
       </c>
       <c r="K23" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="3">
+        <v>44</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>30</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="K24" s="3">
-        <v>31</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>44</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>30</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="K25" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>37</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>27</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="K26" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>34</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>24</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="K27" s="3">
-        <v>76</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>32</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>23</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="K28" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>30</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>23</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="K29" s="3">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>30</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3">
-        <v>23</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="K30" s="3">
-        <v>71</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>30</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>20</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="K31" s="3">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>30</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>20</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="K32" s="3">
-        <v>11</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>211</v>
+        <v>68</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="K34" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>223</v>
+        <v>135</v>
       </c>
       <c r="K35" s="3">
-        <v>16</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="K36" s="3">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="K37" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>236</v>
+        <v>135</v>
       </c>
       <c r="K38" s="3">
-        <v>22</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>20</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="3">
-        <v>13</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K39" s="3">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3">
+        <v>20</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E40" s="3">
-        <v>13</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="G40" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
@@ -3857,10 +3830,10 @@
         <v>241</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="K40" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -3868,34 +3841,34 @@
         <v>242</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>244</v>
+        <v>89</v>
       </c>
       <c r="K41" s="3">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3906,19 +3879,19 @@
         <v>246</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>247</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
@@ -3927,10 +3900,10 @@
         <v>248</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K42" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -3941,54 +3914,54 @@
         <v>250</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>20</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="3">
-        <v>13</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K43" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>17</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="3">
-        <v>13</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
@@ -3997,7 +3970,7 @@
         <v>257</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="K44" s="3">
         <v>8</v>
@@ -4014,28 +3987,28 @@
         <v>260</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>262</v>
+        <v>89</v>
       </c>
       <c r="K45" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4046,124 +4019,124 @@
         <v>264</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3">
+        <v>17</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="3">
-        <v>10</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="J46" s="3" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="K46" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>10</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="K47" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>92</v>
+        <v>271</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="D49" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
@@ -4172,91 +4145,91 @@
         <v>277</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>83</v>
+        <v>278</v>
       </c>
       <c r="K49" s="3">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>279</v>
+        <v>153</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="K50" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>285</v>
+        <v>130</v>
       </c>
       <c r="K51" s="3">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>101</v>
+        <v>287</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>92</v>
+        <v>289</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4265,33 +4238,33 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>66</v>
       </c>
       <c r="K52" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>270</v>
+        <v>75</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4300,150 +4273,150 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>291</v>
+        <v>49</v>
       </c>
       <c r="K53" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>293</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>295</v>
+        <v>95</v>
       </c>
       <c r="K54" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>182</v>
+        <v>298</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>244</v>
+        <v>49</v>
       </c>
       <c r="K55" s="3">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>299</v>
+        <v>113</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>303</v>
+        <v>66</v>
       </c>
       <c r="K56" s="3">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>305</v>
+        <v>86</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
@@ -4452,7 +4425,7 @@
         <v>306</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -4460,25 +4433,25 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E58" s="3">
-        <v>6</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="G58" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
@@ -4487,7 +4460,7 @@
         <v>309</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4498,45 +4471,45 @@
         <v>310</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>182</v>
+        <v>311</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="K59" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>312</v>
+        <v>258</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4545,33 +4518,33 @@
         <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="K60" s="3">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4580,33 +4553,33 @@
         <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="K61" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4615,33 +4588,33 @@
         <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>291</v>
+        <v>117</v>
       </c>
       <c r="K62" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>195</v>
+        <v>323</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4650,30 +4623,30 @@
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K63" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>325</v>
@@ -4688,7 +4661,7 @@
         <v>326</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
@@ -4700,7 +4673,7 @@
         <v>49</v>
       </c>
       <c r="K64" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4711,7 +4684,7 @@
         <v>329</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4720,10 +4693,10 @@
         <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
@@ -4732,231 +4705,231 @@
         <v>331</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>332</v>
+        <v>206</v>
       </c>
       <c r="K65" s="3">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E66" s="3">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="J66" s="3" t="s">
-        <v>227</v>
+        <v>89</v>
       </c>
       <c r="K66" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>6</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" s="3">
-        <v>4</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="J67" s="3" t="s">
-        <v>340</v>
+        <v>49</v>
       </c>
       <c r="K67" s="3">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>342</v>
+        <v>215</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="K68" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E69" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>348</v>
+        <v>101</v>
       </c>
       <c r="K69" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>350</v>
+        <v>91</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E70" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K70" s="3">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>354</v>
+        <v>264</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>256</v>
+        <v>69</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E71" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="K71" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>144</v>
+        <v>349</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4965,33 +4938,33 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="K72" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -5000,33 +4973,33 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="J73" s="3" t="s">
-        <v>95</v>
+        <v>356</v>
       </c>
       <c r="K73" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>25</v>
@@ -5035,33 +5008,33 @@
         <v>3</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>262</v>
+        <v>356</v>
       </c>
       <c r="K74" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>195</v>
+        <v>361</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>92</v>
+        <v>363</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>25</v>
@@ -5070,162 +5043,59 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>66</v>
+        <v>269</v>
       </c>
       <c r="K75" s="3">
-        <v>67</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I76" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="3">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="J76" s="3" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="K76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E77" s="3">
-        <v>3</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K77" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E78" s="3">
-        <v>0</v>
-      </c>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K78" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E79" s="3">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K79" s="3">
-        <v>66</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K79"/>
+  <autoFilter ref="A1:K76"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5302,9 +5172,6 @@
     <hyperlink ref="I74" r:id="rId73"/>
     <hyperlink ref="I75" r:id="rId74"/>
     <hyperlink ref="I76" r:id="rId75"/>
-    <hyperlink ref="I77" r:id="rId76"/>
-    <hyperlink ref="I78" r:id="rId77"/>
-    <hyperlink ref="I79" r:id="rId78"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5312,8 +5179,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -5335,10 +5202,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -5346,190 +5213,259 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>245</v>
+        <v>152</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>274</v>
+        <v>153</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>271</v>
+        <v>154</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>275</v>
+        <v>155</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>278</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>245</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>304</v>
+        <v>210</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>301</v>
+        <v>212</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>306</v>
+        <v>213</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>308</v>
+        <v>85</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>321</v>
+        <v>250</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>301</v>
+        <v>251</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>322</v>
+        <v>252</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>323</v>
+        <v>258</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>324</v>
+        <v>259</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>326</v>
+        <v>261</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>327</v>
+        <v>262</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>368</v>
+        <v>263</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>369</v>
+        <v>264</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>355</v>
+        <v>261</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>370</v>
+        <v>265</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5539,6 +5475,9 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5553,178 +5492,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>234</v>
+        <v>359</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>390</v>
+        <v>272</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -5744,10 +5683,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
@@ -5755,10 +5694,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3">
@@ -5766,10 +5705,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
@@ -5777,10 +5716,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5">
@@ -5791,7 +5730,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6">
@@ -5802,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -5823,13 +5762,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2">
@@ -5837,10 +5776,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5849,10 +5788,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5864,7 +5803,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="D4" s="3"/>
     </row>
